--- a/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -809,7 +809,7 @@
     <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>6641d6b812268c850b4ee551edf04bed</t>
+    <t>b71a9b775a88adbd66165482eac073ee</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -818,7 +818,7 @@
     <t>03_Cluster_groups/Muscle_strength/04_Set_Contrasts/c_data/set_tests.rds</t>
   </si>
   <si>
-    <t>e0f1b73a5db2c5c68cf0842a249d8960</t>
+    <t>c3c35e87f9ae9f6a9412d96f8c8a33bf</t>
   </si>
   <si>
     <t>gene_sets</t>
@@ -827,7 +827,7 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>00_Input/phenotype.csv</t>
@@ -839,7 +839,7 @@
     <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>744c39cf4dab24626dc073a55fe25388</t>
+    <t>0ee2a40846a15c9fa1a6ed51f1f59e4f</t>
   </si>
   <si>
     <t>groups</t>

--- a/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -107,7 +107,7 @@
     <t>arm</t>
   </si>
   <si>
-    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster arc.</t>
+    <t>Study group of the participant (HR or LR), or the cluster that replaces it in a cluster grouping.</t>
   </si>
   <si>
     <t>group</t>
@@ -809,7 +809,7 @@
     <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>b71a9b775a88adbd66165482eac073ee</t>
+    <t>9ceaf25af4bf3a4fb7b194ec8ad6fa8d</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -824,7 +824,7 @@
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>
@@ -839,16 +839,16 @@
     <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>0ee2a40846a15c9fa1a6ed51f1f59e4f</t>
-  </si>
-  <si>
-    <t>groups</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/inputs/groups.rds</t>
-  </si>
-  <si>
-    <t>f3203ca3dfff0a8d6f2c393ba24fd790</t>
+    <t>b038901c2929474ef45746823d122c1e</t>
+  </si>
+  <si>
+    <t>design</t>
+  </si>
+  <si>
+    <t>03_Cluster_groups/Muscle_strength/02_Design_Contrasts/c_data/design.rds</t>
+  </si>
+  <si>
+    <t>c0cfb05785ba25feadb966caf1fa5a50</t>
   </si>
   <si>
     <t>BiocGenerics</t>

--- a/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/03_Cluster_groups/Muscle_strength/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -809,7 +809,7 @@
     <t>03_Cluster_groups/Muscle_strength/03_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>9ceaf25af4bf3a4fb7b194ec8ad6fa8d</t>
+    <t>021f6f1989b638082df99df6839be132</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -839,7 +839,7 @@
     <t>03_Cluster_groups/Muscle_strength/01_Clustering/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>b038901c2929474ef45746823d122c1e</t>
+    <t>810ad67589d07d350257d7bfb5834a74</t>
   </si>
   <si>
     <t>design</t>
